--- a/results/5105_gauss.xlsx
+++ b/results/5105_gauss.xlsx
@@ -413,87 +413,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0</v>
+        <v>-3.255</v>
       </c>
       <c r="B1" t="n">
-        <v>41.24593826362935</v>
+        <v>11.31096302868533</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4185</v>
+        <v>-2.8985</v>
       </c>
       <c r="B2" t="n">
-        <v>40.26935940379511</v>
+        <v>30.21164309139379</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.837</v>
+        <v>-2.542</v>
       </c>
       <c r="B3" t="n">
-        <v>39.58836893738389</v>
+        <v>69.87506678109116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.2555</v>
+        <v>-2.17</v>
       </c>
       <c r="B4" t="n">
-        <v>34.34192890002449</v>
+        <v>139.3203188991124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.674</v>
+        <v>-1.8135</v>
       </c>
       <c r="B5" t="n">
-        <v>25.00382361950596</v>
+        <v>232.362131976762</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.0925</v>
+        <v>-1.457</v>
       </c>
       <c r="B6" t="n">
-        <v>16.43759404299101</v>
+        <v>342.3700638136892</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.511</v>
+        <v>-1.085</v>
       </c>
       <c r="B7" t="n">
-        <v>12.47826580299157</v>
+        <v>456.0211702987992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.9295</v>
+        <v>-0.7285</v>
       </c>
       <c r="B8" t="n">
-        <v>5.714381313758683</v>
+        <v>547.9022262851421</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.348</v>
+        <v>-0.372</v>
       </c>
       <c r="B9" t="n">
-        <v>2.563140671789906</v>
+        <v>609.4242147930748</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.782</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1.456628593742876</v>
+        <v>634.0449426558846</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="B11" t="n">
+        <v>620.4463922059822</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="B12" t="n">
+        <v>572.1770077953229</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.9145</v>
+      </c>
+      <c r="B13" t="n">
+        <v>491.0189200068376</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1.2245</v>
+      </c>
+      <c r="B14" t="n">
+        <v>381.4269591559432</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.5345</v>
+      </c>
+      <c r="B15" t="n">
+        <v>260.1425447966993</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1.8445</v>
+      </c>
+      <c r="B16" t="n">
+        <v>149.8194262656861</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2.1545</v>
+      </c>
+      <c r="B17" t="n">
+        <v>71.18002485857232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2.4645</v>
+      </c>
+      <c r="B18" t="n">
+        <v>29.37035572602846</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.7745</v>
+      </c>
+      <c r="B19" t="n">
+        <v>11.66976640955722</v>
       </c>
     </row>
   </sheetData>

--- a/results/5105_gauss.xlsx
+++ b/results/5105_gauss.xlsx
@@ -418,66 +418,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-3.255</v>
+        <v>-3.3015</v>
       </c>
       <c r="B1" t="n">
-        <v>11.31096302868533</v>
+        <v>9.830585557436745</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-2.8985</v>
+        <v>-2.945</v>
       </c>
       <c r="B2" t="n">
-        <v>30.21164309139379</v>
+        <v>26.85509039583682</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-2.542</v>
+        <v>-2.573</v>
       </c>
       <c r="B3" t="n">
-        <v>69.87506678109116</v>
+        <v>65.3072283504407</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-2.17</v>
+        <v>-2.201</v>
       </c>
       <c r="B4" t="n">
-        <v>139.3203188991124</v>
+        <v>132.413765833636</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.8135</v>
+        <v>-1.8445</v>
       </c>
       <c r="B5" t="n">
-        <v>232.362131976762</v>
+        <v>223.2894016359663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.457</v>
+        <v>-1.4725</v>
       </c>
       <c r="B6" t="n">
-        <v>342.3700638136892</v>
+        <v>337.6692284955211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.085</v>
+        <v>-1.1005</v>
       </c>
       <c r="B7" t="n">
-        <v>456.0211702987992</v>
+        <v>451.3680459089603</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.7285</v>
+        <v>-0.744</v>
       </c>
       <c r="B8" t="n">
-        <v>547.9022262851421</v>
+        <v>544.3919286861914</v>
       </c>
     </row>
     <row r="9">
@@ -485,7 +485,7 @@
         <v>-0.372</v>
       </c>
       <c r="B9" t="n">
-        <v>609.4242147930748</v>
+        <v>609.4242242190305</v>
       </c>
     </row>
     <row r="10">
@@ -493,79 +493,79 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>634.0449426558846</v>
+        <v>634.0449517257487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.2945</v>
+        <v>0.31</v>
       </c>
       <c r="B11" t="n">
-        <v>620.4463922059822</v>
+        <v>618.9425582940395</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.6045</v>
+        <v>0.62</v>
       </c>
       <c r="B12" t="n">
-        <v>572.1770077953229</v>
+        <v>568.6049374401069</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.9145</v>
+        <v>0.9455</v>
       </c>
       <c r="B13" t="n">
-        <v>491.0189200068376</v>
+        <v>481.4603323607381</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.2245</v>
+        <v>1.2555</v>
       </c>
       <c r="B14" t="n">
-        <v>381.4269591559432</v>
+        <v>369.5774116107743</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.5345</v>
+        <v>1.5655</v>
       </c>
       <c r="B15" t="n">
-        <v>260.1425447966993</v>
+        <v>248.1852610724177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.8445</v>
+        <v>1.891</v>
       </c>
       <c r="B16" t="n">
-        <v>149.8194262656861</v>
+        <v>135.9397946384849</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2.1545</v>
+        <v>2.201</v>
       </c>
       <c r="B17" t="n">
-        <v>71.18002485857232</v>
+        <v>62.89713828192603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.4645</v>
+        <v>2.511</v>
       </c>
       <c r="B18" t="n">
-        <v>29.37035572602846</v>
+        <v>25.50336462198305</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.7745</v>
+        <v>2.8365</v>
       </c>
       <c r="B19" t="n">
-        <v>11.66976640955722</v>
+        <v>9.727539017928271</v>
       </c>
     </row>
   </sheetData>

--- a/results/5105_gauss.xlsx
+++ b/results/5105_gauss.xlsx
@@ -418,74 +418,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-3.3015</v>
+        <v>-2.976</v>
       </c>
       <c r="B1" t="n">
-        <v>9.830585557436745</v>
+        <v>9.815171746556047</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-2.945</v>
+        <v>-2.6505</v>
       </c>
       <c r="B2" t="n">
-        <v>26.85509039583682</v>
+        <v>14.77457143566392</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-2.573</v>
+        <v>-2.325</v>
       </c>
       <c r="B3" t="n">
-        <v>65.3072283504407</v>
+        <v>20.27093881011646</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-2.201</v>
+        <v>-1.984</v>
       </c>
       <c r="B4" t="n">
-        <v>132.413765833636</v>
+        <v>25.35786280548246</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.8445</v>
+        <v>-1.6585</v>
       </c>
       <c r="B5" t="n">
-        <v>223.2894016359663</v>
+        <v>28.86592201773007</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.4725</v>
+        <v>-1.333</v>
       </c>
       <c r="B6" t="n">
-        <v>337.6692284955211</v>
+        <v>31.20723557798038</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.1005</v>
+        <v>-0.992</v>
       </c>
       <c r="B7" t="n">
-        <v>451.3680459089603</v>
+        <v>32.65168198679562</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.744</v>
+        <v>-0.6665</v>
       </c>
       <c r="B8" t="n">
-        <v>544.3919286861914</v>
+        <v>34.04412371377345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.372</v>
+        <v>-0.341</v>
       </c>
       <c r="B9" t="n">
-        <v>609.4242242190305</v>
+        <v>35.12198333022383</v>
       </c>
     </row>
     <row r="10">
@@ -493,79 +493,79 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>634.0449517257487</v>
+        <v>34.88547289061877</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.31</v>
+        <v>0.2635</v>
       </c>
       <c r="B11" t="n">
-        <v>618.9425582940395</v>
+        <v>33.79854113666399</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.62</v>
+        <v>0.527</v>
       </c>
       <c r="B12" t="n">
-        <v>568.6049374401069</v>
+        <v>32.74252586981872</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.9455</v>
+        <v>0.7905</v>
       </c>
       <c r="B13" t="n">
-        <v>481.4603323607381</v>
+        <v>33.42671387686886</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.2555</v>
+        <v>1.054</v>
       </c>
       <c r="B14" t="n">
-        <v>369.5774116107743</v>
+        <v>30.64598010322211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.5655</v>
+        <v>1.3175</v>
       </c>
       <c r="B15" t="n">
-        <v>248.1852610724177</v>
+        <v>27.34646384940539</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.891</v>
+        <v>1.581</v>
       </c>
       <c r="B16" t="n">
-        <v>135.9397946384849</v>
+        <v>21.6447125708245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2.201</v>
+        <v>1.8445</v>
       </c>
       <c r="B17" t="n">
-        <v>62.89713828192603</v>
+        <v>16.38315854501352</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.511</v>
+        <v>2.108</v>
       </c>
       <c r="B18" t="n">
-        <v>25.50336462198305</v>
+        <v>12.14197076929219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.8365</v>
+        <v>2.387</v>
       </c>
       <c r="B19" t="n">
-        <v>9.727539017928271</v>
+        <v>9.497028992433862</v>
       </c>
     </row>
   </sheetData>
